--- a/atop-20260419095608/atop_20260418.xlsx
+++ b/atop-20260419095608/atop_20260418.xlsx
@@ -89926,6 +89926,9 @@
       <c r="B120">
         <v>3.3266666666666667</v>
       </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
@@ -89934,6 +89937,9 @@
       <c r="B121">
         <v>3.85</v>
       </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
@@ -89942,6 +89948,9 @@
       <c r="B122">
         <v>3.8366666666666664</v>
       </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
@@ -89950,6 +89959,9 @@
       <c r="B123">
         <v>3.88</v>
       </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
@@ -89958,6 +89970,9 @@
       <c r="B124">
         <v>3.91</v>
       </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
@@ -89966,6 +89981,9 @@
       <c r="B125">
         <v>3.9466666666666668</v>
       </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
@@ -89974,6 +89992,9 @@
       <c r="B126">
         <v>3.9133333333333336</v>
       </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
@@ -89982,6 +90003,9 @@
       <c r="B127">
         <v>3.8666666666666667</v>
       </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
@@ -89990,6 +90014,9 @@
       <c r="B128">
         <v>3.283333333333333</v>
       </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
@@ -89998,6 +90025,9 @@
       <c r="B129">
         <v>4.16</v>
       </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
@@ -90006,6 +90036,9 @@
       <c r="B130">
         <v>4.1</v>
       </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
@@ -90014,6 +90047,9 @@
       <c r="B131">
         <v>4.176666666666667</v>
       </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
@@ -90022,6 +90058,9 @@
       <c r="B132">
         <v>4.116666666666666</v>
       </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
@@ -90030,6 +90069,9 @@
       <c r="B133">
         <v>4.006666666666667</v>
       </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
@@ -90038,6 +90080,9 @@
       <c r="B134">
         <v>3.973333333333333</v>
       </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
@@ -90046,6 +90091,9 @@
       <c r="B135">
         <v>3.9433333333333334</v>
       </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
@@ -90054,6 +90102,9 @@
       <c r="B136">
         <v>3.9233333333333333</v>
       </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
@@ -90062,6 +90113,9 @@
       <c r="B137">
         <v>4.086666666666667</v>
       </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
@@ -90070,6 +90124,9 @@
       <c r="B138">
         <v>3.973333333333333</v>
       </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
@@ -90078,6 +90135,9 @@
       <c r="B139">
         <v>4.066666666666666</v>
       </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
@@ -90086,6 +90146,9 @@
       <c r="B140">
         <v>4.073333333333333</v>
       </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
@@ -90094,6 +90157,9 @@
       <c r="B141">
         <v>4.21</v>
       </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
@@ -90102,6 +90168,9 @@
       <c r="B142">
         <v>4.173333333333333</v>
       </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
@@ -90110,6 +90179,9 @@
       <c r="B143">
         <v>4.1433333333333335</v>
       </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
@@ -90118,6 +90190,9 @@
       <c r="B144">
         <v>4.12</v>
       </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
@@ -90126,6 +90201,9 @@
       <c r="B145">
         <v>4.39</v>
       </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
@@ -90134,6 +90212,9 @@
       <c r="B146">
         <v>4.266666666666667</v>
       </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
@@ -90142,6 +90223,9 @@
       <c r="B147">
         <v>4.11</v>
       </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
@@ -90150,6 +90234,9 @@
       <c r="B148">
         <v>4.093333333333334</v>
       </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
@@ -90158,6 +90245,9 @@
       <c r="B149">
         <v>4.236666666666666</v>
       </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
@@ -90166,6 +90256,9 @@
       <c r="B150">
         <v>4.21</v>
       </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
@@ -90174,6 +90267,9 @@
       <c r="B151">
         <v>4.296666666666667</v>
       </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
@@ -90182,6 +90278,9 @@
       <c r="B152">
         <v>4.246666666666667</v>
       </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
@@ -90190,6 +90289,9 @@
       <c r="B153">
         <v>4.246666666666667</v>
       </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
@@ -90198,6 +90300,9 @@
       <c r="B154">
         <v>4.166666666666667</v>
       </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
@@ -90206,6 +90311,9 @@
       <c r="B155">
         <v>4.07</v>
       </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
@@ -90214,6 +90322,9 @@
       <c r="B156">
         <v>3.43</v>
       </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
@@ -90222,6 +90333,9 @@
       <c r="B157">
         <v>3.5966666666666667</v>
       </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
@@ -90230,6 +90344,9 @@
       <c r="B158">
         <v>3.19</v>
       </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
@@ -90238,6 +90355,9 @@
       <c r="B159">
         <v>3.236666666666667</v>
       </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
@@ -90246,6 +90366,9 @@
       <c r="B160">
         <v>3.296666666666667</v>
       </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
@@ -90254,6 +90377,9 @@
       <c r="B161">
         <v>3.243333333333333</v>
       </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
@@ -90262,6 +90388,9 @@
       <c r="B162">
         <v>3.236666666666667</v>
       </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
@@ -90270,6 +90399,9 @@
       <c r="B163">
         <v>3.35</v>
       </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
@@ -90278,6 +90410,9 @@
       <c r="B164">
         <v>3.3266666666666667</v>
       </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
@@ -90286,6 +90421,9 @@
       <c r="B165">
         <v>3.6633333333333336</v>
       </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
@@ -90294,6 +90432,9 @@
       <c r="B166">
         <v>3.4133333333333336</v>
       </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
@@ -90302,6 +90443,9 @@
       <c r="B167">
         <v>3.4166666666666665</v>
       </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
@@ -90310,6 +90454,9 @@
       <c r="B168">
         <v>3.38</v>
       </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
@@ -90318,6 +90465,9 @@
       <c r="B169">
         <v>3.86</v>
       </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
@@ -90326,6 +90476,9 @@
       <c r="B170">
         <v>3.97</v>
       </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
@@ -90334,6 +90487,9 @@
       <c r="B171">
         <v>4.073333333333333</v>
       </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
@@ -90342,6 +90498,9 @@
       <c r="B172">
         <v>3.6733333333333333</v>
       </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
@@ -90350,6 +90509,9 @@
       <c r="B173">
         <v>4.123333333333333</v>
       </c>
+      <c r="C173">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
@@ -90358,6 +90520,9 @@
       <c r="B174">
         <v>4.04</v>
       </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
@@ -90366,6 +90531,9 @@
       <c r="B175">
         <v>4.046666666666667</v>
       </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
@@ -90374,6 +90542,9 @@
       <c r="B176">
         <v>3.3933333333333335</v>
       </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
@@ -90382,6 +90553,9 @@
       <c r="B177">
         <v>4.033333333333333</v>
       </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
@@ -90390,6 +90564,9 @@
       <c r="B178">
         <v>4.053333333333334</v>
       </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
@@ -90398,6 +90575,9 @@
       <c r="B179">
         <v>4.1466666666666665</v>
       </c>
+      <c r="C179">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
@@ -90406,6 +90586,9 @@
       <c r="B180">
         <v>4.12</v>
       </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
@@ -90414,6 +90597,9 @@
       <c r="B181">
         <v>4.133333333333334</v>
       </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
@@ -90422,6 +90608,9 @@
       <c r="B182">
         <v>4.046666666666667</v>
       </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
@@ -90430,6 +90619,9 @@
       <c r="B183">
         <v>4.1</v>
       </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
@@ -90438,6 +90630,9 @@
       <c r="B184">
         <v>4.046666666666667</v>
       </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
@@ -90446,6 +90641,9 @@
       <c r="B185">
         <v>4.136666666666667</v>
       </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
@@ -90454,6 +90652,9 @@
       <c r="B186">
         <v>4.12</v>
       </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
@@ -90462,6 +90663,9 @@
       <c r="B187">
         <v>4.04</v>
       </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
@@ -90470,6 +90674,9 @@
       <c r="B188">
         <v>4.173333333333333</v>
       </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
@@ -90489,6 +90696,9 @@
       <c r="B190">
         <v>4.183333333333334</v>
       </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
@@ -90497,6 +90707,9 @@
       <c r="B191">
         <v>4.233333333333333</v>
       </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
@@ -90505,6 +90718,9 @@
       <c r="B192">
         <v>4.196666666666666</v>
       </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
@@ -90513,6 +90729,9 @@
       <c r="B193">
         <v>4.23</v>
       </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
@@ -90521,6 +90740,9 @@
       <c r="B194">
         <v>4.11</v>
       </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
@@ -90529,6 +90751,9 @@
       <c r="B195">
         <v>4.156666666666666</v>
       </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
@@ -90537,6 +90762,9 @@
       <c r="B196">
         <v>4.116666666666666</v>
       </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
@@ -90545,6 +90773,9 @@
       <c r="B197">
         <v>4.113333333333333</v>
       </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
@@ -90553,6 +90784,9 @@
       <c r="B198">
         <v>4.1866666666666665</v>
       </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
@@ -90561,6 +90795,9 @@
       <c r="B199">
         <v>4.156666666666666</v>
       </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
@@ -90569,6 +90806,9 @@
       <c r="B200">
         <v>4.126666666666667</v>
       </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
@@ -90577,6 +90817,9 @@
       <c r="B201">
         <v>4.18</v>
       </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
@@ -90585,6 +90828,9 @@
       <c r="B202">
         <v>4.123333333333333</v>
       </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
@@ -90593,6 +90839,9 @@
       <c r="B203">
         <v>4.273333333333333</v>
       </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
@@ -90601,6 +90850,9 @@
       <c r="B204">
         <v>4.286666666666667</v>
       </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
@@ -90609,6 +90861,9 @@
       <c r="B205">
         <v>4.35</v>
       </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
@@ -90617,6 +90872,9 @@
       <c r="B206">
         <v>4.203333333333333</v>
       </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
@@ -90625,6 +90883,9 @@
       <c r="B207">
         <v>4.263333333333334</v>
       </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
@@ -90633,6 +90894,9 @@
       <c r="B208">
         <v>4.076666666666667</v>
       </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
@@ -90641,6 +90905,9 @@
       <c r="B209">
         <v>4.286666666666667</v>
       </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
@@ -90649,6 +90916,9 @@
       <c r="B210">
         <v>4.233333333333333</v>
       </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
@@ -90657,6 +90927,9 @@
       <c r="B211">
         <v>4.183333333333334</v>
       </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
@@ -90665,6 +90938,9 @@
       <c r="B212">
         <v>4.16</v>
       </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
@@ -90673,6 +90949,9 @@
       <c r="B213">
         <v>4.226666666666667</v>
       </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
@@ -90681,6 +90960,9 @@
       <c r="B214">
         <v>4.236666666666666</v>
       </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
@@ -90689,6 +90971,9 @@
       <c r="B215">
         <v>4.323333333333333</v>
       </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
@@ -90697,6 +90982,9 @@
       <c r="B216">
         <v>4.253333333333333</v>
       </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
@@ -90705,6 +90993,9 @@
       <c r="B217">
         <v>4.35</v>
       </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
@@ -90713,6 +91004,9 @@
       <c r="B218">
         <v>4.3133333333333335</v>
       </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
@@ -90721,6 +91015,9 @@
       <c r="B219">
         <v>4.2</v>
       </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
@@ -90729,6 +91026,9 @@
       <c r="B220">
         <v>4.226666666666667</v>
       </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
@@ -90737,6 +91037,9 @@
       <c r="B221">
         <v>4.223333333333334</v>
       </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
@@ -90745,6 +91048,9 @@
       <c r="B222">
         <v>4.273333333333333</v>
       </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
@@ -90753,6 +91059,9 @@
       <c r="B223">
         <v>4.246666666666667</v>
       </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
@@ -90761,6 +91070,9 @@
       <c r="B224">
         <v>4.203333333333333</v>
       </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
@@ -90769,6 +91081,9 @@
       <c r="B225">
         <v>3.5866666666666664</v>
       </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
@@ -90777,6 +91092,9 @@
       <c r="B226">
         <v>3.4633333333333334</v>
       </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
@@ -90785,6 +91103,9 @@
       <c r="B227">
         <v>3.6233333333333335</v>
       </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
@@ -90793,6 +91114,9 @@
       <c r="B228">
         <v>3.566666666666667</v>
       </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
@@ -90801,6 +91125,9 @@
       <c r="B229">
         <v>3.5566666666666666</v>
       </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
@@ -90809,6 +91136,9 @@
       <c r="B230">
         <v>3.546666666666667</v>
       </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
@@ -90817,6 +91147,9 @@
       <c r="B231">
         <v>3.566666666666667</v>
       </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
@@ -90825,6 +91158,9 @@
       <c r="B232">
         <v>3.54</v>
       </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
@@ -90833,6 +91169,9 @@
       <c r="B233">
         <v>3.5633333333333335</v>
       </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
@@ -90841,6 +91180,9 @@
       <c r="B234">
         <v>3.4833333333333334</v>
       </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
@@ -90849,6 +91191,9 @@
       <c r="B235">
         <v>3.466666666666667</v>
       </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
@@ -90857,6 +91202,9 @@
       <c r="B236">
         <v>3.433333333333333</v>
       </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
@@ -90865,6 +91213,9 @@
       <c r="B237">
         <v>3.6166666666666667</v>
       </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
@@ -90873,6 +91224,9 @@
       <c r="B238">
         <v>4.11</v>
       </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
@@ -90881,6 +91235,9 @@
       <c r="B239">
         <v>4.11</v>
       </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
@@ -90889,6 +91246,9 @@
       <c r="B240">
         <v>4.166666666666667</v>
       </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
@@ -90897,6 +91257,9 @@
       <c r="B241">
         <v>4.216666666666667</v>
       </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
@@ -90905,6 +91268,9 @@
       <c r="B242">
         <v>3.53</v>
       </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
@@ -90913,6 +91279,9 @@
       <c r="B243">
         <v>4.08</v>
       </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
@@ -90921,6 +91290,9 @@
       <c r="B244">
         <v>4.136666666666667</v>
       </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
@@ -90929,6 +91301,9 @@
       <c r="B245">
         <v>4.213333333333333</v>
       </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
@@ -90937,6 +91312,9 @@
       <c r="B246">
         <v>4.136666666666667</v>
       </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
@@ -90945,6 +91323,9 @@
       <c r="B247">
         <v>4.18</v>
       </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
@@ -90953,6 +91334,9 @@
       <c r="B248">
         <v>4.14</v>
       </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
@@ -90961,6 +91345,9 @@
       <c r="B249">
         <v>4.203333333333333</v>
       </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
@@ -90969,6 +91356,9 @@
       <c r="B250">
         <v>4.113333333333333</v>
       </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
@@ -90977,6 +91367,9 @@
       <c r="B251">
         <v>4.206666666666667</v>
       </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
@@ -90985,6 +91378,9 @@
       <c r="B252">
         <v>4.093333333333334</v>
       </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
@@ -90993,6 +91389,9 @@
       <c r="B253">
         <v>4.163333333333333</v>
       </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
@@ -91001,6 +91400,9 @@
       <c r="B254">
         <v>4.07</v>
       </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
@@ -91009,6 +91411,9 @@
       <c r="B255">
         <v>4.073333333333333</v>
       </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
@@ -91017,6 +91422,9 @@
       <c r="B256">
         <v>4.11</v>
       </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
@@ -91025,6 +91433,9 @@
       <c r="B257">
         <v>4.17</v>
       </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
@@ -91033,6 +91444,9 @@
       <c r="B258">
         <v>4.1433333333333335</v>
       </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
@@ -91041,6 +91455,9 @@
       <c r="B259">
         <v>4.1466666666666665</v>
       </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
@@ -91049,6 +91466,9 @@
       <c r="B260">
         <v>4.113333333333333</v>
       </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
@@ -91057,6 +91477,9 @@
       <c r="B261">
         <v>4.28</v>
       </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
@@ -91065,6 +91488,9 @@
       <c r="B262">
         <v>4.246666666666667</v>
       </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
@@ -91073,6 +91499,9 @@
       <c r="B263">
         <v>4.176666666666667</v>
       </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
@@ -91081,6 +91510,9 @@
       <c r="B264">
         <v>4.126666666666667</v>
       </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
@@ -91089,6 +91521,9 @@
       <c r="B265">
         <v>3.7666666666666666</v>
       </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
@@ -91097,6 +91532,9 @@
       <c r="B266">
         <v>3.6133333333333333</v>
       </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
@@ -91105,6 +91543,9 @@
       <c r="B267">
         <v>3.8566666666666665</v>
       </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
@@ -91113,6 +91554,9 @@
       <c r="B268">
         <v>3.486666666666667</v>
       </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
@@ -91121,6 +91565,9 @@
       <c r="B269">
         <v>3.5566666666666666</v>
       </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
@@ -91129,6 +91576,9 @@
       <c r="B270">
         <v>3.54</v>
       </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
@@ -91137,6 +91587,9 @@
       <c r="B271">
         <v>3.5833333333333335</v>
       </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
@@ -91145,6 +91598,9 @@
       <c r="B272">
         <v>3.57</v>
       </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
@@ -91153,6 +91609,9 @@
       <c r="B273">
         <v>3.5533333333333332</v>
       </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
@@ -91161,6 +91620,9 @@
       <c r="B274">
         <v>3.54</v>
       </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
@@ -91169,6 +91631,9 @@
       <c r="B275">
         <v>3.6033333333333335</v>
       </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
@@ -91177,6 +91642,9 @@
       <c r="B276">
         <v>3.6</v>
       </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
@@ -91185,6 +91653,9 @@
       <c r="B277">
         <v>3.7533333333333334</v>
       </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
@@ -91193,6 +91664,9 @@
       <c r="B278">
         <v>3.54</v>
       </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
@@ -91201,6 +91675,9 @@
       <c r="B279">
         <v>3.5733333333333333</v>
       </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
@@ -91209,6 +91686,9 @@
       <c r="B280">
         <v>3.47</v>
       </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
@@ -91217,6 +91697,9 @@
       <c r="B281">
         <v>3.513333333333333</v>
       </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
@@ -91225,6 +91708,9 @@
       <c r="B282">
         <v>3.4633333333333334</v>
       </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
@@ -91233,6 +91719,9 @@
       <c r="B283">
         <v>3.493333333333333</v>
       </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
@@ -91241,6 +91730,9 @@
       <c r="B284">
         <v>3.4366666666666665</v>
       </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
@@ -91249,6 +91741,9 @@
       <c r="B285">
         <v>3.4</v>
       </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
@@ -91257,6 +91752,9 @@
       <c r="B286">
         <v>3.45</v>
       </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
@@ -91265,6 +91763,9 @@
       <c r="B287">
         <v>3.45</v>
       </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
@@ -91273,6 +91774,9 @@
       <c r="B288">
         <v>3.4033333333333333</v>
       </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
@@ -91281,6 +91785,9 @@
       <c r="B289">
         <v>3.4033333333333333</v>
       </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
@@ -91289,6 +91796,9 @@
       <c r="B290">
         <v>3.3466666666666667</v>
       </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
@@ -91297,6 +91807,9 @@
       <c r="B291">
         <v>3.2666666666666666</v>
       </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
@@ -91305,6 +91818,9 @@
       <c r="B292">
         <v>3.2533333333333334</v>
       </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
@@ -91312,6 +91828,9 @@
       </c>
       <c r="B293">
         <v>3.2866666666666666</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -91321,6 +91840,9 @@
       <c r="B294">
         <v>3.2666666666666666</v>
       </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
@@ -91329,6 +91851,9 @@
       <c r="B295">
         <v>3.223333333333333</v>
       </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
@@ -91337,6 +91862,9 @@
       <c r="B296">
         <v>3.1466666666666665</v>
       </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
@@ -91345,6 +91873,9 @@
       <c r="B297">
         <v>3.24</v>
       </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
@@ -91353,6 +91884,9 @@
       <c r="B298">
         <v>3.1666666666666665</v>
       </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
@@ -91361,6 +91895,9 @@
       <c r="B299">
         <v>2.8333333333333335</v>
       </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
@@ -91369,6 +91906,9 @@
       <c r="B300">
         <v>2.8266666666666667</v>
       </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
@@ -91377,6 +91917,9 @@
       <c r="B301">
         <v>2.88</v>
       </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
@@ -91385,6 +91928,9 @@
       <c r="B302">
         <v>2.9566666666666666</v>
       </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
@@ -91393,6 +91939,9 @@
       <c r="B303">
         <v>2.9966666666666666</v>
       </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
@@ -91401,6 +91950,9 @@
       <c r="B304">
         <v>2.8633333333333333</v>
       </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
@@ -91409,6 +91961,9 @@
       <c r="B305">
         <v>2.8266666666666667</v>
       </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
@@ -91417,6 +91972,9 @@
       <c r="B306">
         <v>2.816666666666667</v>
       </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
@@ -91425,6 +91983,9 @@
       <c r="B307">
         <v>2.8266666666666667</v>
       </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
@@ -91432,6 +91993,9 @@
       </c>
       <c r="B308">
         <v>2.81</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
